--- a/00001/Lista_Octava_Tres_de_Mayo.xlsx
+++ b/00001/Lista_Octava_Tres_de_Mayo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\OneDrive\Documentos\Liga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D0D3BC8-7D25-47D5-AF77-6029404CBC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C689C1D1-8730-47ED-A1EC-FE0DFEF98EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0A98E24E-32CF-423C-8AA4-D8C52A5BBBF0}"/>
   </bookViews>
@@ -148,7 +148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -198,25 +198,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,16 +562,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -589,629 +585,629 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>53944965</v>
       </c>
-      <c r="D2" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E2">
         <v>111</v>
       </c>
-      <c r="F2" s="6">
-        <v>7</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>53488374</v>
       </c>
-      <c r="D3" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E3" s="6">
-        <v>112</v>
-      </c>
-      <c r="F3" s="6">
-        <v>7</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="D3" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E3">
+        <v>1129</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>53487907</v>
       </c>
-      <c r="D4" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E4" s="6">
-        <v>113</v>
-      </c>
-      <c r="F4" s="6">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="D4" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E4">
+        <v>1130</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>53662554</v>
       </c>
-      <c r="D5" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E5">
         <v>114</v>
       </c>
-      <c r="F5" s="6">
-        <v>7</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
         <v>53942387</v>
       </c>
-      <c r="D6" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E6">
         <v>115</v>
       </c>
-      <c r="F6" s="6">
-        <v>7</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>53663010</v>
       </c>
-      <c r="D7" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E7">
         <v>116</v>
       </c>
-      <c r="F7" s="6">
-        <v>7</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
         <v>53488202</v>
       </c>
-      <c r="D8" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E8" s="6">
-        <v>117</v>
-      </c>
-      <c r="F8" s="6">
-        <v>7</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="D8" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E8">
+        <v>1131</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>53660790</v>
       </c>
-      <c r="D9" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E9" s="6">
-        <v>118</v>
-      </c>
-      <c r="F9" s="6">
-        <v>7</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="D9" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E9">
+        <v>1132</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>53489872</v>
       </c>
-      <c r="D10" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E10" s="6">
-        <v>119</v>
-      </c>
-      <c r="F10" s="6">
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="D10" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E10">
+        <v>1133</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>53488001</v>
       </c>
-      <c r="D11" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E11">
         <v>1110</v>
       </c>
-      <c r="F11" s="6">
-        <v>7</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>54538531</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>42005</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12">
         <v>1111</v>
       </c>
-      <c r="F12" s="6">
-        <v>7</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>53947880</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>42005</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13">
         <v>1112</v>
       </c>
-      <c r="F13" s="6">
-        <v>7</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>55257652</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>42370</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14">
         <v>1113</v>
       </c>
-      <c r="F14" s="6">
-        <v>7</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>55920215</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>42370</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15">
         <v>1114</v>
       </c>
-      <c r="F15" s="6">
-        <v>7</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="F15">
+        <v>7</v>
+      </c>
+      <c r="G15">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>54541908</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>42005</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16">
         <v>1115</v>
       </c>
-      <c r="F16" s="6">
-        <v>7</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>56085381</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>42736</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17">
         <v>1116</v>
       </c>
-      <c r="F17" s="6">
-        <v>7</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="G17">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>54924417</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>42005</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18">
         <v>1117</v>
       </c>
-      <c r="F18" s="6">
-        <v>7</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>56290113</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>42736</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19">
         <v>1118</v>
       </c>
-      <c r="F19" s="6">
-        <v>7</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>53490920</v>
       </c>
-      <c r="D20" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E20">
         <v>1119</v>
       </c>
-      <c r="F20" s="6">
-        <v>7</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>53658269</v>
       </c>
-      <c r="D21" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E21">
         <v>1120</v>
       </c>
-      <c r="F21" s="6">
-        <v>7</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>55384571</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>42370</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22">
         <v>1121</v>
       </c>
-      <c r="F22" s="6">
-        <v>7</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>54169078</v>
       </c>
-      <c r="D23" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="D23" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E23">
         <v>1122</v>
       </c>
-      <c r="F23" s="6">
-        <v>7</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>55925523</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>42736</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24">
         <v>1123</v>
       </c>
-      <c r="F24" s="6">
-        <v>7</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>54538481</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>42005</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25">
         <v>1124</v>
       </c>
-      <c r="F25" s="6">
-        <v>7</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>54439677</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>42005</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26">
         <v>1125</v>
       </c>
-      <c r="F26" s="6">
-        <v>7</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>27</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>53946110</v>
       </c>
-      <c r="D27" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="D27" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E27">
         <v>1127</v>
       </c>
-      <c r="F27" s="6">
-        <v>7</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>54167647</v>
       </c>
-      <c r="D28" s="5">
-        <v>41640</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="D28" s="4">
+        <v>41640</v>
+      </c>
+      <c r="E28">
         <v>1128</v>
       </c>
-      <c r="F28" s="6">
-        <v>7</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
         <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E29" t="str">
-        <f t="shared" ref="E3:E29" si="0">CONCATENATE(F29,A29)</f>
+        <f t="shared" ref="E29" si="0">CONCATENATE(F29,A29)</f>
         <v/>
       </c>
     </row>

--- a/00001/Lista_Octava_Tres_de_Mayo.xlsx
+++ b/00001/Lista_Octava_Tres_de_Mayo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\OneDrive\Documentos\Liga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C689C1D1-8730-47ED-A1EC-FE0DFEF98EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85587C31-8963-4C8D-9344-3F2218609CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0A98E24E-32CF-423C-8AA4-D8C52A5BBBF0}"/>
   </bookViews>
@@ -598,7 +598,7 @@
         <v>41640</v>
       </c>
       <c r="E2">
-        <v>111</v>
+        <v>1134</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -713,7 +713,7 @@
         <v>41640</v>
       </c>
       <c r="E7">
-        <v>116</v>
+        <v>1135</v>
       </c>
       <c r="F7">
         <v>7</v>
